--- a/figures_v14/figures_v14.xlsx
+++ b/figures_v14/figures_v14.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>Figure 2 - predicted vs true RUL, FD001. Points on the diagonal are perfect. The LLM forms horizontal bands: its output does not depend on the engine.</t>
   </si>
@@ -141,19 +141,22 @@
 (6 conditions)</t>
   </si>
   <si>
-    <t>Figure 5 - explanations agree with the textbook, not with the data. Source: results_p0/p0_2a_report.md</t>
+    <t>Figure 5 - what the stated direction agrees with, per sensor. Sources: results_p0/p0_2a_report.md and results_p1/p3_5_report.md</t>
   </si>
   <si>
     <t>Sensor</t>
   </si>
   <si>
-    <t>Agreement with textbook direction (%)</t>
+    <t>Agrees with the direction the prompt asserts (%)</t>
   </si>
   <si>
-    <t>Faithfulness to the input window (%)</t>
+    <t>Agrees with the direction the data shows (%)</t>
   </si>
   <si>
-    <t>Base rate: canonical direction present (%)</t>
+    <t>Agrees with the window supplied (%)</t>
+  </si>
+  <si>
+    <t>Base rate, same claims (%)</t>
   </si>
   <si>
     <t>n claims</t>
@@ -405,12 +408,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Predicted vs true RUL, FD001 (100 engines)</a:t>
@@ -3045,12 +3048,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>True RUL (cycles)</a:t>
@@ -3074,7 +3077,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -3109,12 +3112,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Predicted RUL (cycles)</a:t>
@@ -3138,7 +3141,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -3164,7 +3167,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -3201,12 +3204,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Distribution of predicted RUL, FD001 (100 engines)</a:t>
@@ -3239,8 +3242,10 @@
             <a:solidFill>
               <a:srgbClr val="1F3B57"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3357,8 +3362,10 @@
             <a:solidFill>
               <a:srgbClr val="4E8FA8"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3475,8 +3482,10 @@
             <a:solidFill>
               <a:srgbClr val="9FC5D4"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3593,8 +3602,10 @@
             <a:solidFill>
               <a:srgbClr val="C2553F"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3711,8 +3722,10 @@
             <a:solidFill>
               <a:srgbClr val="8C8C8C"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3829,8 +3842,10 @@
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -3946,12 +3961,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Predicted RUL (cycles)</a:t>
@@ -3974,7 +3989,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4010,12 +4025,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Number of engines</a:t>
@@ -4039,7 +4054,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4065,7 +4080,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -4102,12 +4117,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Distinct predicted values and modal share by sub-dataset (zero-shot, n = 30)</a:t>
@@ -4360,12 +4375,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Dataset</a:t>
@@ -4388,7 +4403,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4424,12 +4439,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Distinct values / engines</a:t>
@@ -4453,7 +4468,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4479,12 +4494,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Modal share (%)</a:t>
@@ -4501,7 +4516,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4541,7 +4556,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -4578,15 +4593,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Directional claims per sensor: textbook agreement, input faithfulness, base rate</a:t>
+              <a:t>Directional claims per sensor: what the stated direction agrees with</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4607,7 +4622,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Agreement with textbook direction (%)</c:v>
+                  <c:v>Agrees with the direction the prompt asserts (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4616,8 +4631,10 @@
             <a:solidFill>
               <a:srgbClr val="1F3B57"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -4689,7 +4706,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Faithfulness to the input window (%)</c:v>
+                  <c:v>Agrees with the direction the data shows (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4698,8 +4715,10 @@
             <a:solidFill>
               <a:srgbClr val="C2553F"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -4738,25 +4757,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49.25925925925926</c:v>
+                  <c:v>51.11111111111111</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27.07622298065984</c:v>
+                  <c:v>4.436860068259386</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>62.09081309398099</c:v>
+                  <c:v>98.41605068637803</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.24857685009488</c:v>
+                  <c:v>21.25237191650854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.70809578107183</c:v>
+                  <c:v>3.420752565564424</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56.86274509803921</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4771,7 +4790,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Base rate: canonical direction present (%)</c:v>
+                  <c:v>Agrees with the window supplied (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4780,8 +4799,10 @@
             <a:solidFill>
               <a:srgbClr val="9FC5D4"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -4820,25 +4841,109 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>62.11111111111111</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.14814814814815</c:v>
+                  <c:v>49.25925925925926</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.18518518518518</c:v>
+                  <c:v>27.07622298065984</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>61.14814814814815</c:v>
+                  <c:v>62.09081309398099</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.25925925925926</c:v>
+                  <c:v>47.24857685009488</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.81481481481481</c:v>
+                  <c:v>27.70809578107183</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60.14814814814815</c:v>
+                  <c:v>56.86274509803921</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DATI_fig5!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Base rate, same claims (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8C8C8C"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>DATI_fig5!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>s4 (not cued)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>s7 (not cued)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>s9 (cued)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>s11 (cued)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>s12 (cued)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>s14 (cued)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>s15 (cued)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DATI_fig5!$E$4:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49.62962962962963</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.50739476678044</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62.19640971488912</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.93548387096774</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.93614595210946</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56.86274509803921</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4861,12 +4966,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Sensor (cued = named in the prompt)</a:t>
@@ -4889,7 +4994,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4926,12 +5031,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Percentage of directional claims</a:t>
@@ -4955,7 +5060,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -4981,7 +5086,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -5018,12 +5123,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Paired trend reversals and the claims that followed them (2.4%)</a:t>
@@ -5056,8 +5161,10 @@
             <a:solidFill>
               <a:srgbClr val="1F3B57"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -5132,8 +5239,10 @@
             <a:solidFill>
               <a:srgbClr val="C2553F"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:cat>
@@ -5207,12 +5316,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Sensor</a:t>
@@ -5235,7 +5344,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -5271,12 +5380,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Number of (engine, sensor) pairs</a:t>
@@ -5300,7 +5409,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -5326,7 +5435,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -5363,12 +5472,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Mean predicted RUL versus mean RUL of the few-shot examples (n = 7, r = 0.94)</a:t>
@@ -5590,12 +5699,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Mean RUL of the examples placed in the prompt</a:t>
@@ -5619,7 +5728,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -5654,12 +5763,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Mean predicted RUL (100 engines)</a:t>
@@ -5683,7 +5792,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -5709,7 +5818,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" baseline="0">
+            <a:defRPr sz="1100" baseline="0">
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -5746,12 +5855,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" baseline="0">
+              <a:defRPr sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Rank correlation with the true RUL (FD001)</a:t>
@@ -5977,12 +6086,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" baseline="0">
+                  <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Spearman rho</a:t>
@@ -6006,7 +6115,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" baseline="0">
+              <a:defRPr sz="1100" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
@@ -8327,26 +8436,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -8360,7 +8469,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>39.4</v>
@@ -8374,7 +8483,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3">
         <v>60</v>
@@ -8388,7 +8497,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3">
         <v>62.8</v>
@@ -8402,7 +8511,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3">
         <v>87.40000000000001</v>
@@ -8416,7 +8525,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3">
         <v>99.2</v>
@@ -8430,7 +8539,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3">
         <v>101.2</v>
@@ -8468,24 +8577,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -8493,7 +8602,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>-0.2107777272579729</v>
@@ -8513,7 +8622,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3">
         <v>0.0268566269780988</v>
@@ -8533,7 +8642,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3">
         <v>0.0276311892564081</v>
@@ -8553,7 +8662,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3">
         <v>0.0515350411981689</v>
@@ -8573,7 +8682,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3">
         <v>0.0547709260357429</v>
@@ -8593,7 +8702,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3">
         <v>0.0554564170785257</v>
@@ -8613,7 +8722,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>0.0699104924278693</v>
@@ -8633,7 +8742,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3">
         <v>0.1150591523632716</v>
@@ -8653,7 +8762,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3">
         <v>0.1407821157098359</v>
@@ -8673,7 +8782,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3">
         <v>0.1842360347286281</v>
@@ -8693,7 +8802,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3">
         <v>0.2103369438616555</v>
@@ -8713,7 +8822,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3">
         <v>0.2134199268903652</v>
@@ -8733,7 +8842,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3">
         <v>0.2403850786990348</v>
@@ -8753,7 +8862,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="3">
         <v>0.2612514963110097</v>
@@ -8773,7 +8882,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3">
         <v>0.2936431555628189</v>
@@ -8793,7 +8902,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -9273,19 +9382,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="5" width="14.7109375" customWidth="1"/>
+    <col min="2" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -9301,123 +9410,147 @@
       <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>60</v>
       </c>
       <c r="C4" s="3">
+        <v>60</v>
+      </c>
+      <c r="D4" s="3">
         <v>50</v>
       </c>
-      <c r="D4" s="3">
-        <v>62.11111111111111</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>51.11111111111111</v>
       </c>
       <c r="C5" s="3">
+        <v>51.11111111111111</v>
+      </c>
+      <c r="D5" s="3">
         <v>49.25925925925926</v>
       </c>
-      <c r="D5" s="3">
-        <v>47.14814814814815</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
+        <v>49.62962962962963</v>
+      </c>
+      <c r="F5" s="4">
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3">
         <v>95.56313993174061</v>
       </c>
       <c r="C6" s="3">
+        <v>4.436860068259386</v>
+      </c>
+      <c r="D6" s="3">
         <v>27.07622298065984</v>
       </c>
-      <c r="D6" s="3">
-        <v>26.18518518518518</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
+        <v>26.50739476678044</v>
+      </c>
+      <c r="F6" s="4">
         <v>879</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3">
         <v>98.41605068637803</v>
       </c>
       <c r="C7" s="3">
+        <v>98.41605068637803</v>
+      </c>
+      <c r="D7" s="3">
         <v>62.09081309398099</v>
       </c>
-      <c r="D7" s="3">
-        <v>61.14814814814815</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
+        <v>62.19640971488912</v>
+      </c>
+      <c r="F7" s="4">
         <v>947</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3">
         <v>78.74762808349146</v>
       </c>
       <c r="C8" s="3">
+        <v>21.25237191650854</v>
+      </c>
+      <c r="D8" s="3">
         <v>47.24857685009488</v>
       </c>
-      <c r="D8" s="3">
-        <v>42.25925925925926</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
+        <v>41.93548387096774</v>
+      </c>
+      <c r="F8" s="4">
         <v>527</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>96.57924743443557</v>
       </c>
       <c r="C9" s="3">
+        <v>3.420752565564424</v>
+      </c>
+      <c r="D9" s="3">
         <v>27.70809578107183</v>
       </c>
-      <c r="D9" s="3">
-        <v>27.81481481481481</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
+        <v>27.93614595210946</v>
+      </c>
+      <c r="F9" s="4">
         <v>877</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3">
         <v>100</v>
       </c>
       <c r="C10" s="3">
+        <v>100</v>
+      </c>
+      <c r="D10" s="3">
         <v>56.86274509803921</v>
       </c>
-      <c r="D10" s="3">
-        <v>60.14814814814815</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
+        <v>56.86274509803921</v>
+      </c>
+      <c r="F10" s="4">
         <v>306</v>
       </c>
     </row>
@@ -9447,7 +9580,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9455,15 +9588,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>77</v>
@@ -9474,7 +9607,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>94</v>
@@ -9485,7 +9618,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>12</v>
@@ -9496,7 +9629,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>68</v>
@@ -9507,7 +9640,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>2</v>
@@ -9518,7 +9651,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>253</v>

--- a/figures_v14/figures_v14.xlsx
+++ b/figures_v14/figures_v14.xlsx
@@ -126,19 +126,19 @@
   </si>
   <si>
     <t>FD001
-(1 condition)</t>
+1 condition, 100 engines</t>
   </si>
   <si>
     <t>FD003
-(1 condition)</t>
+1 condition, 100 engines</t>
   </si>
   <si>
     <t>FD002
-(6 conditions)</t>
+6 conditions, 259 engines</t>
   </si>
   <si>
     <t>FD004
-(6 conditions)</t>
+6 conditions, 248 engines</t>
   </si>
   <si>
     <t>Figure 5 - what the stated direction agrees with, per sensor. Sources: results_p0/p0_2a_report.md and results_p1/p3_5_report.md</t>
@@ -4125,7 +4125,7 @@
               <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Distinct predicted values and modal share by sub-dataset (zero-shot, n = 30)</a:t>
+              <a:t>Share of predictions on a single value, by sub-dataset (zero-shot, n = 30)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4142,11 +4142,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>DATI_fig4!$B$3</c:f>
+              <c:f>DATI_fig4!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Distinct predicted values</c:v>
+                  <c:v>Modal share (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4155,10 +4155,99 @@
             <a:solidFill>
               <a:srgbClr val="1F3B57"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3A3A3A"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>2 values</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>2 values</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>4 values</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>4 values</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:numFmt formatCode="0" sourceLinked="0"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="1F3B57"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showVal val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>DATI_fig4!$A$4:$A$7</c:f>
@@ -4166,172 +4255,19 @@
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>FD001
-(1 condition)</c:v>
+1 condition, 100 engines</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>FD003
-(1 condition)</c:v>
+1 condition, 100 engines</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>FD002
-(6 conditions)</c:v>
+6 conditions, 259 engines</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>FD004
-(6 conditions)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>DATI_fig4!$B$4:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>DATI_fig4!$D$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Engines</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="9FC5D4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>DATI_fig4!$A$4:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>FD001
-(1 condition)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>FD003
-(1 condition)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>FD002
-(6 conditions)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>FD004
-(6 conditions)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>DATI_fig4!$D$4:$D$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>259</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="70"/>
-        <c:axId val="50030001"/>
-        <c:axId val="50030002"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>DATI_fig4!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Modal share (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400">
-              <a:solidFill>
-                <a:srgbClr val="C2553F"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C2553F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>DATI_fig4!$A$4:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>FD001
-(1 condition)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>FD003
-(1 condition)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>FD002
-(6 conditions)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>FD004
-(6 conditions)</c:v>
+6 conditions, 248 engines</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4358,10 +4294,10 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
-        <c:axId val="60030001"/>
-        <c:axId val="60030002"/>
-      </c:lineChart>
+        <c:gapWidth val="80"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:barChart>
       <c:catAx>
         <c:axId val="50030001"/>
         <c:scaling>
@@ -4383,7 +4319,7 @@
                   <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Dataset</a:t>
+                  <a:t>Sub-dataset</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -4419,8 +4355,9 @@
       <c:valAx>
         <c:axId val="50030002"/>
         <c:scaling>
-          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines>
@@ -4447,14 +4384,14 @@
                   <a:rPr lang="en-US" sz="1100" baseline="0">
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Distinct values / engines</a:t>
+                  <a:t>Predictions on the modal value (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
@@ -4479,68 +4416,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="60030002"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="100"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:axPos val="r"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" vert="horz"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Modal share (%)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="60030001"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:catAx>
-        <c:axId val="60030001"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="60030002"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -4548,22 +4423,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>

--- a/figures_v14/figures_v14.xlsx
+++ b/figures_v14/figures_v14.xlsx
@@ -5026,6 +5026,24 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="1F3B57"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showVal val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>DATI_fig6!$A$4:$A$9</c:f>
@@ -5104,6 +5122,126 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>1 (1%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>0 (0%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>3 (25%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>2 (3%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>0 (0%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>6 (2%)</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="1F3B57"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showVal val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>DATI_fig6!$A$4:$A$9</c:f>
@@ -5381,6 +5519,143 @@
               </a:ln>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>asis_seed1</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>strat_seed3</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>strat_seed2</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>strat_seed1</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>random_seed2</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>random_seed1</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>random_seed3</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="8C8C8C"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+          </c:dLbls>
           <c:trendline>
             <c:name>Linear fit</c:name>
             <c:spPr>
